--- a/data/ranking_away_base_TOP200_LIMPO.xlsx
+++ b/data/ranking_away_base_TOP200_LIMPO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anderson\Documents\GitHub\Skynet-V18\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590E5D7D-220A-48E7-A7F0-69330FD6F3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38302EE0-8740-4286-B9ED-439F3F53981E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17160" yWindow="-120" windowWidth="19440" windowHeight="11760" xr2:uid="{2643A559-0D65-4E4A-B138-4A65A82F8B0D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="17520" windowHeight="13200" xr2:uid="{2643A559-0D65-4E4A-B138-4A65A82F8B0D}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -6841,7 +6841,7 @@
         <v>17</v>
       </c>
       <c r="O71" t="s">
-        <v>23</v>
+        <v>210</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
